--- a/Data/Battery.xlsx
+++ b/Data/Battery.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Campus-Application/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA793E23-4BDC-7241-8C74-65DA87D67FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E77690-6496-E140-AA24-E12CAF539146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
   </bookViews>
@@ -38,15 +38,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>Metrics</t>
   </si>
   <si>
     <t>Initial Cost</t>
-  </si>
-  <si>
-    <t>Initial Efficiency</t>
   </si>
   <si>
     <t>Initial Emission</t>
@@ -469,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5344E307-70EA-9749-BC3D-54A83804696F}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.33203125" bestFit="1" customWidth="1"/>
@@ -480,7 +477,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -498,15 +495,15 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -514,7 +511,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -522,26 +519,27 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>0.01</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
       <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <f>(1-0.58)/15</f>
+        <v>2.8000000000000004E-2</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -549,27 +547,26 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <f>(1-0.58)/15</f>
-        <v>2.8000000000000004E-2</v>
-      </c>
+        <f>B2*0.58</f>
+        <v>290</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
-        <f>B2*0.58</f>
-        <v>290</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>20</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -577,7 +574,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>6.1000000000000004E-3</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -585,14 +582,6 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>6.1000000000000004E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14">
         <v>1</v>
       </c>
     </row>
@@ -623,18 +612,18 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>11</v>
-      </c>
-      <c r="D1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0.25</v>
@@ -648,7 +637,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0.73422939532219</v>
@@ -662,7 +651,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>0.101601938183078</v>
@@ -676,7 +665,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>0.479875110533934</v>
@@ -690,7 +679,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>1.1069427523737401</v>
@@ -704,7 +693,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -743,15 +732,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
         <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0.33333333333333331</v>
@@ -762,7 +751,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>0.13241354364108079</v>
@@ -773,7 +762,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>6.1105499694598393E-2</v>
@@ -784,7 +773,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>0.87597866475830377</v>
@@ -795,7 +784,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>1.0630110556133701</v>
@@ -806,7 +795,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>0</v>

--- a/Data/Battery.xlsx
+++ b/Data/Battery.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Campus-Application/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E77690-6496-E140-AA24-E12CAF539146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24952559-38EB-B245-8ACF-63538D5FF961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" activeTab="2" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial values" sheetId="7" r:id="rId1"/>
@@ -113,6 +113,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -148,10 +151,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -626,13 +630,13 @@
         <v>3</v>
       </c>
       <c r="B2">
+        <v>0.46428571428571402</v>
+      </c>
+      <c r="C2">
         <v>0.25</v>
       </c>
-      <c r="C2">
-        <v>0.33333333333333298</v>
-      </c>
       <c r="D2">
-        <v>0.41666666666666702</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -640,13 +644,13 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>0.73422939532219</v>
+        <v>0.3934364978676097</v>
       </c>
       <c r="C3">
-        <v>0.13241354364108099</v>
+        <v>0.85669513598587532</v>
       </c>
       <c r="D3">
-        <v>0.53482430784430701</v>
+        <v>1.184675179225112</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -654,13 +658,13 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>0.101601938183078</v>
+        <v>0.14118239703995239</v>
       </c>
       <c r="C4">
-        <v>6.11054996945984E-2</v>
+        <v>0.29974579339722113</v>
       </c>
       <c r="D4">
-        <v>0.135870147279403</v>
+        <v>0.23582856445071071</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -668,13 +672,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.479875110533934</v>
+        <v>0.67473416327462576</v>
       </c>
       <c r="C5">
-        <v>0.87597866475830399</v>
+        <v>0.42456288891842348</v>
       </c>
       <c r="D5">
-        <v>0.58577219668457303</v>
+        <v>0.30584550834081797</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -682,13 +686,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.1069427523737401</v>
+        <v>1.151634683586618</v>
       </c>
       <c r="C6">
-        <v>1.0630110556133701</v>
+        <v>1.3495157081652129</v>
       </c>
       <c r="D6">
-        <v>1.1455331333427099</v>
+        <v>1.265957261483982</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -743,10 +747,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>0.33333333333333331</v>
+        <v>0.53571428571428603</v>
       </c>
       <c r="C2">
-        <v>0.66666666666666663</v>
+        <v>0.46428571428571402</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -754,10 +758,10 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>0.13241354364108079</v>
+        <v>0.41592802130109002</v>
       </c>
       <c r="C3">
-        <v>0.59403413835682428</v>
+        <v>1.0881243682498001</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -765,10 +769,10 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>6.1105499694598393E-2</v>
+        <v>0.14911648635566349</v>
       </c>
       <c r="C4">
-        <v>0.13249018794714751</v>
+        <v>0.27515142062759301</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -776,10 +780,10 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.87597866475830377</v>
+        <v>0.65972775512087578</v>
       </c>
       <c r="C5">
-        <v>0.55209555635010954</v>
+        <v>0.33684770381107798</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -787,10 +791,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.0630110556133701</v>
-      </c>
-      <c r="C6">
-        <v>1.1416678139292959</v>
+        <v>1.160808199650649</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1.316730039862261</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">

--- a/Data/Battery.xlsx
+++ b/Data/Battery.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Campus-Application/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24952559-38EB-B245-8ACF-63538D5FF961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5567B94A-ED43-AE44-BB09-67F12E8BB2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" activeTab="2" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial values" sheetId="7" r:id="rId1"/>
@@ -630,13 +630,13 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>0.46428571428571402</v>
+        <v>0.42857142857142799</v>
       </c>
       <c r="C2">
         <v>0.25</v>
       </c>
       <c r="D2">
-        <v>0.2857142857142857</v>
+        <v>0.32142857142857101</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -644,13 +644,13 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>0.3934364978676097</v>
+        <v>0.39225442482365303</v>
       </c>
       <c r="C3">
-        <v>0.85669513598587532</v>
+        <v>0.79106624697365602</v>
       </c>
       <c r="D3">
-        <v>1.184675179225112</v>
+        <v>1.1431921420637501</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -658,13 +658,13 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>0.14118239703995239</v>
+        <v>0.213476816662999</v>
       </c>
       <c r="C4">
-        <v>0.29974579339722113</v>
+        <v>0.236683163073998</v>
       </c>
       <c r="D4">
-        <v>0.23582856445071071</v>
+        <v>0.246350074303059</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -672,13 +672,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.67473416327462576</v>
+        <f>EXP(-B3)</f>
+        <v>0.6755322199285716</v>
       </c>
       <c r="C5">
-        <v>0.42456288891842348</v>
+        <f t="shared" ref="C5:D5" si="0">EXP(-C3)</f>
+        <v>0.45336114253533677</v>
       </c>
       <c r="D5">
-        <v>0.30584550834081797</v>
+        <f t="shared" si="0"/>
+        <v>0.31879974177284642</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -686,13 +689,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.151634683586618</v>
+        <f>EXP(B4)</f>
+        <v>1.2379747975484678</v>
       </c>
       <c r="C6">
-        <v>1.3495157081652129</v>
+        <f t="shared" ref="C6:D6" si="1">EXP(C4)</f>
+        <v>1.2670396092373635</v>
       </c>
       <c r="D6">
-        <v>1.265957261483982</v>
+        <f t="shared" si="1"/>
+        <v>1.2793473617936353</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -747,7 +753,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>0.53571428571428603</v>
+        <v>0.53571428571428503</v>
       </c>
       <c r="C2">
         <v>0.46428571428571402</v>
@@ -758,10 +764,10 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>0.41592802130109002</v>
+        <v>0.45507553413483898</v>
       </c>
       <c r="C3">
-        <v>1.0881243682498001</v>
+        <v>1.05440770945111</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -769,21 +775,23 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>0.14911648635566349</v>
+        <v>0.19271163505334099</v>
       </c>
       <c r="C4">
-        <v>0.27515142062759301</v>
+        <v>0.27271143777690698</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>0.65972775512087578</v>
+      <c r="B5" s="3">
+        <f>EXP(-B3)</f>
+        <v>0.63440004727971477</v>
       </c>
       <c r="C5">
-        <v>0.33684770381107798</v>
+        <f>EXP(-C3)</f>
+        <v>0.34839871947650675</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -791,10 +799,12 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.160808199650649</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1.316730039862261</v>
+        <f>EXP(B4)</f>
+        <v>1.2125330910604515</v>
+      </c>
+      <c r="C6">
+        <f>EXP(C4)</f>
+        <v>1.3135211575469345</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">

--- a/Data/Battery.xlsx
+++ b/Data/Battery.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Campus-Application/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5567B94A-ED43-AE44-BB09-67F12E8BB2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0935ECE1-133C-D744-9761-9C6F07D23BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial values" sheetId="7" r:id="rId1"/>
@@ -507,7 +507,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -578,7 +578,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>6.1000000000000004E-3</v>
+        <v>8.6999999999999994E-3</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
